--- a/PCBNo.10081/PCBNo.10081/SP0557_rev02_00_AI2/SP0557_rev02_00_AI/修正履歴.xlsx
+++ b/PCBNo.10081/PCBNo.10081/SP0557_rev02_00_AI2/SP0557_rev02_00_AI/修正履歴.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/512e22ffcc52695f/ドキュメント/GitHub/PCBNo.10081/PCBNo.10081/PCBNo.10081/SP0557_rev02_00_AI (1)/SP0557_rev02_00_AI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/512e22ffcc52695f/ドキュメント/GitHub/PCBNo.10081/PCBNo.10081/PCBNo.10081/SP0557_rev02_00_AI2/SP0557_rev02_00_AI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{D598A26E-3CE0-478B-8CBA-B84AEA3FEF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A5FCCE2-A761-43A7-A4D8-20111421A258}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="8_{D598A26E-3CE0-478B-8CBA-B84AEA3FEF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0B775DA-2830-4F60-8C29-E9562C8BBC8B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="4" xr2:uid="{3A2BB469-6CC5-41C3-8C98-63503D4CF60C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="6" xr2:uid="{3A2BB469-6CC5-41C3-8C98-63503D4CF60C}"/>
   </bookViews>
   <sheets>
     <sheet name="修正履歴" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="No3" sheetId="4" r:id="rId4"/>
     <sheet name="No4" sheetId="5" r:id="rId5"/>
     <sheet name="No5" sheetId="7" r:id="rId6"/>
+    <sheet name="No6" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="676">
   <si>
     <t>No</t>
     <phoneticPr fontId="1"/>
@@ -3918,12 +3919,990 @@
       <t xml:space="preserve"> にコミット・プッシュ</t>
     </r>
   </si>
+  <si>
+    <t>S3IO通信ブロックにおいて、LE占有率80%時に通信エラーが発生し、20%に落とすとエラーが消失する問題。前回セッションでCLKに対するタイミング制約（.lpf FREQUENCY/MULTICYCLE/BLOCK PATH + .fdc define_clock）を追加したが、エラーは解消されていない。</t>
+  </si>
+  <si>
+    <t>根本原因分析</t>
+  </si>
+  <si>
+    <t>原因1（致命的）: Synplify合成時にFDC制約が適用されていない</t>
+  </si>
+  <si>
+    <t>@W: MT420 |Found inferred clock pll_gen|CLKOS2_inferred_clock with period 5.00ns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         Please declare a user-defined clock on net slv_com_top_inst.clk_gen_inst2.PLL_inst.s_PLL_CLK20M.</t>
+  </si>
+  <si>
+    <t>@W: MT529 |Found inferred clock pll_gen|CLKOS2_inferred_clock which controls 8628 sequential elements...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         This clock has no specified timing constraint...</t>
+  </si>
+  <si>
+    <t>全5クロックがデフォルト200MHz（5ns）として推定されている：</t>
+  </si>
+  <si>
+    <t>PLL出力</t>
+  </si>
+  <si>
+    <t>実際の周波数</t>
+  </si>
+  <si>
+    <t>Synplify推定</t>
+  </si>
+  <si>
+    <t>結果</t>
+  </si>
+  <si>
+    <t>CLKOS2 (s_PLL_CLK20M)</t>
+  </si>
+  <si>
+    <t>20MHz</t>
+  </si>
+  <si>
+    <t>200MHz</t>
+  </si>
+  <si>
+    <t>FAIL (-4.054ns)</t>
+  </si>
+  <si>
+    <t>CLKOS3 (CLK1)</t>
+  </si>
+  <si>
+    <t>10MHz</t>
+  </si>
+  <si>
+    <t>FAIL (-5.533ns)</t>
+  </si>
+  <si>
+    <t>CLKOP (CLKCOM_OUT/CLK2)</t>
+  </si>
+  <si>
+    <t>100MHz</t>
+  </si>
+  <si>
+    <t>PASS (+0.890ns)</t>
+  </si>
+  <si>
+    <t>CLKOS (CLK2A)</t>
+  </si>
+  <si>
+    <t>PASS (+1.923ns)</t>
+  </si>
+  <si>
+    <t>原因2（致命的）: 全PLLクロックが別クロックグループとして扱われている</t>
+  </si>
+  <si>
+    <t>pll_gen|CLKOS2_inferred_clock → pll_gen|CLKOS3_inferred_clock : Diff grp (NOT ANALYZED)</t>
+  </si>
+  <si>
+    <t>pll_gen|CLKOS_inferred_clock  → pll_gen|CLKOP_inferred_clock  : Diff grp (NOT ANALYZED)</t>
+  </si>
+  <si>
+    <t>pll_gen|CLKOP_inferred_clock  → pll_gen|CLKOS3_inferred_clock : Diff grp (NOT ANALYZED)</t>
+  </si>
+  <si>
+    <t>sdc</t>
+  </si>
+  <si>
+    <t>define_clock -name {pll_gen|CLKOS2_inferred_clock} ... -clockgroup Autoconstr_clkgroup_0</t>
+  </si>
+  <si>
+    <t>define_clock -name {pll_gen|CLKOP_inferred_clock}  ... -clockgroup Autoconstr_clkgroup_3</t>
+  </si>
+  <si>
+    <t>define_clock -name {pll_gen|CLKOS_inferred_clock}  ... -clockgroup Autoconstr_clkgroup_2</t>
+  </si>
+  <si>
+    <t>```</t>
+  </si>
+  <si>
+    <t>**影響**: CLK2(CLKOP) ↔ CLK2A(CLKOS) 間のパスがタイミング解析の対象外。cds.vhdのCDRサンプリングパスが完全に無制約。</t>
+  </si>
+  <si>
+    <t>### 原因3（重大）: cds.vhd の CLK2↔CLK2A クロスドメインパスが無制約</t>
+  </si>
+  <si>
+    <t>cds.vhd は4位相サンプリングでCDR（Clock Data Recovery）を行う：</t>
+  </si>
+  <si>
+    <t>- Domain A: CLK2立上り（0°）→ az(0)</t>
+  </si>
+  <si>
+    <t>- Domain B: CLK2A立上り（90°）→ bz(0) → **CLK2で再サンプリング** bz(1)</t>
+  </si>
+  <si>
+    <t>- Domain C: CLK2立下り（180°）→ cz(0) → **CLK2Aで再サンプリング** cz(1)</t>
+  </si>
+  <si>
+    <t>- Domain D: CLK2A立下り（270°）→ dz(0) → **CLK2立下りで再サンプリング** dz(1)</t>
+  </si>
+  <si>
+    <t>各ドメイン間転送は最大7.5ns（3/4周期）のマージンがあるが、Synplifyもclk2↔CLK2Aの位相関係を認識していないため、合成時に最適化されない。</t>
+  </si>
+  <si>
+    <t>### 原因4（中程度）: AutoConstraint_SP0557.sdc の誤った周期値</t>
+  </si>
+  <si>
+    <t>自動生成されたSDCファイルの周期値が実際と大幅に乖離：</t>
+  </si>
+  <si>
+    <t>| クロック | SDC自動制約 | 実際 |</t>
+  </si>
+  <si>
+    <t>|---|---|---|</t>
+  </si>
+  <si>
+    <t>| CLKOS2 | 7.885ns (127MHz) | 50ns (20MHz) |</t>
+  </si>
+  <si>
+    <t>| CLKOS3 | 428.169ns (2.3MHz) | 100ns (10MHz) |</t>
+  </si>
+  <si>
+    <t>| CLKOP | 3.493ns (286MHz) | 10ns (100MHz) |</t>
+  </si>
+  <si>
+    <t>| CLKOS | 2.616ns (382MHz) | 10ns (100MHz) |</t>
+  </si>
+  <si>
+    <t>## 修正計画</t>
+  </si>
+  <si>
+    <t>### Step 1: SP0557.fdc の修正（Synplify合成制約）</t>
+  </si>
+  <si>
+    <t>**ファイル**: `SP0557_rev02_00_AI2/SP0557_rev02_00_AI/SP0557/SP0557.fdc`</t>
+  </si>
+  <si>
+    <t>現在の.fdcは周波数のみ定義し、クロックグループ・位相関係・クロスドメインパスが未定義。以下を追加/修正：</t>
+  </si>
+  <si>
+    <t>1. **全PLLクロックを同一クロックグループに配置** → Synplifyが関連クロック間パスを解析対象にする</t>
+  </si>
+  <si>
+    <t>2. **CLK2↔CLK2Aの位相オフセット定義** → 90°位相差を考慮したタイミング解析を有効化</t>
+  </si>
+  <si>
+    <t>3. **クロスドメインパスのマルチサイクル制約** → 実際のデータ転送タイミングに合わせた緩和</t>
+  </si>
+  <si>
+    <t># 全PLLクロックを同一グループ "pll_clks" に配置</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOS2} -freq 20.000 -clockgroup pll_clks {n:slv_com_top_inst.clk_gen_inst2.PLL_inst.s_PLL_CLK20M}</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOP}  -freq 100.000 -clockgroup pll_clks {n:slv_com_top_inst.clk_gen_inst2.PLL_inst.CLKCOM_OUT}</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOS}  -freq 100.000 -clockgroup pll_clks -rise 2.500 -fall 7.500 {n:slv_com_top_inst.clk_gen_inst2.PLL_inst.CLK2A}</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLKOS3} -freq 10.000  -clockgroup pll_clks {n:slv_com_top_inst.clk_gen_inst2.PLL_inst.CLK1}</t>
+  </si>
+  <si>
+    <t>define_clock -name {CLK20M} -freq 20.000 {p:CLK20M}</t>
+  </si>
+  <si>
+    <t>Step 2: AutoConstraint_SP0557.sdc の無効化</t>
+  </si>
+  <si>
+    <t>自動生成SDCは誤った周期値と独立クロックグループを設定しており、FDCの正しい定義と競合する。リネームして無効化する。</t>
+  </si>
+  <si>
+    <t>Step 3: SP0557.lpf の制約追加</t>
+  </si>
+  <si>
+    <t>現在の.lpfに以下を追加：</t>
+  </si>
+  <si>
+    <t>lpf</t>
+  </si>
+  <si>
+    <t># CLK2(CLKOP, 0°) → CLK2A(CLKOS, 90°): launch=0ns, capture=2.5ns → slack=2.5ns</t>
+  </si>
+  <si>
+    <t># これは1周期未満なので制約不要（デフォルトで解析される）</t>
+  </si>
+  <si>
+    <t># CLK2A(CLKOS, 90°) → CLK2(CLKOP, 0°): launch=2.5ns, capture=10ns → slack=7.5ns</t>
+  </si>
+  <si>
+    <t># デフォルトは10ns(1周期)制約。実質7.5ns利用可能なので追加制約不要。</t>
+  </si>
+  <si>
+    <t># ただしPARに位相関係を明示する必要がある → OFFSET制約</t>
+  </si>
+  <si>
+    <t># Lattice Diamond (PAR) はPLLの位相情報をbitstream/primitiveから自動認識するため、</t>
+  </si>
+  <si>
+    <t># FREQUENCY制約がPLLピン名で正しく定義されていれば位相も認識される。</t>
+  </si>
+  <si>
+    <t># ガードバンディング: 100MHz → 115MHz で余裕確保</t>
+  </si>
+  <si>
+    <t>FREQUENCY NET "slv_com_top_inst.CLKCOM_OUT" 115.000000 MHz ;</t>
+  </si>
+  <si>
+    <t>FREQUENCY NET "slv_com_top_inst/CLK2A" 115.000000 MHz ;</t>
+  </si>
+  <si>
+    <t>Step 4: Synplifyプロジェクト設定の確認</t>
+  </si>
+  <si>
+    <t>操作</t>
+  </si>
+  <si>
+    <t>SP0557/SP0557.fdc</t>
+  </si>
+  <si>
+    <t>修正: クロックグループ統一 + 位相オフセット追加</t>
+  </si>
+  <si>
+    <t>SP0557/AutoConstraint_SP0557.sdc</t>
+  </si>
+  <si>
+    <t>リネーム（.sdc.bak）して無効化</t>
+  </si>
+  <si>
+    <t>修正: ガードバンディング追加 (100MHz → 115MHz)</t>
+  </si>
+  <si>
+    <t>1. AutoConstraint_SP0557.sdc を .sdc.bak にリネーム</t>
+  </si>
+  <si>
+    <t>2. SP0557.fdc を修正</t>
+  </si>
+  <si>
+    <t>3. SP0557.lpf を修正</t>
+  </si>
+  <si>
+    <t>4. Synplify で再合成 → automake.log で以下を確認:</t>
+  </si>
+  <si>
+    <t>MT420/MT529 警告が消えていること</t>
+  </si>
+  <si>
+    <t>全クロックが正しい周波数で認識されていること</t>
+  </si>
+  <si>
+    <t>クロスドメインマトリクスで "Diff grp" が表示されないこと（同一グループ）</t>
+  </si>
+  <si>
+    <t>5. Diamond PAR → .twr タイミングレポートで slack &gt; 1.0ns を確認</t>
+  </si>
+  <si>
+    <t>6. 実機テスト → LE占有率80%で通信エラーが発生しないこと</t>
+  </si>
+  <si>
+    <r>
+      <t>証拠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>automake.log</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> の MT420/MT529 警告</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>原因</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>SP0557.fdc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>（前回作成）が合成時に正しく読み込まれていないか、合成がFDC追加前に実行されたもの。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>証拠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>automake.log</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> のクロスドメインマトリクス（行3324-3338）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AutoConstraint_SP0557.sdc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> が各クロックを独立した </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>Autoconstr_clkgroup_0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> ～ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> に配置：</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Key: CLKOSの </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>-rise 2.500 -fall 7.500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> でCLK2Aの90°位相シフト（2.5ns）をSynplifyに伝達。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ファイル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>SP0557_rev02_00_AI2/SP0557_rev02_00_AI/SP0557/AutoConstraint_SP0557.sdc</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ファイル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>SP0557_rev02_00_AI2/SP0557_rev02_00_AI/SP0557.lpf</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. CLK2↔CLK2A間のMULTICYCLE制約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> — PARレベルで位相関係を反映</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. タイミングガードバンディング</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> — 100MHzクロックを110MHzとして制約し、マージン確保</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ファイル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>SP0557_rev02_00_AI2/SP0557_rev02_00_AI/SP0557/SP0557_syn.prj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>set_option -write_apr_constraint 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> が有効。これはSynplifyが自動的にAutoConstraintを書き出す設定。FDCが正しく適用されれば、AutoConstraintも正しい値になるはず。ただし、既存のAutoConstraintファイルが残っていると競合する可能性があるため、合成前に削除/リネームすること。</t>
+    </r>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S3IOの通信異常が発生している原因を調査</t>
+    <rPh sb="5" eb="9">
+      <t>ツウシンイジョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>チョウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイミング制約の問題ではなく、Synplify合成時のクロックグループ設定の問題でした。</t>
+  </si>
+  <si>
+    <t>発見した致命的問題</t>
+  </si>
+  <si>
+    <t>pll_gen|CLKOS2_inferred_clock → Autoconstr_clkgroup_0 (20MHz, 8628 loads)</t>
+  </si>
+  <si>
+    <t>pll_gen|CLKOP_inferred_clock  → Autoconstr_clkgroup_3 (100MHz/CLK2, 258 loads)</t>
+  </si>
+  <si>
+    <t>pll_gen|CLKOS_inferred_clock  → Autoconstr_clkgroup_2 (100MHz/CLK2A, 22 loads)</t>
+  </si>
+  <si>
+    <t>pll_gen|CLKOS3_inferred_clock → Autoconstr_clkgroup_4 (10MHz/CLK1, 545 loads)</t>
+  </si>
+  <si>
+    <t>なぜ前回の.lpf制約が効かなかったか</t>
+  </si>
+  <si>
+    <t>修正内容（3ファイル）</t>
+  </si>
+  <si>
+    <t>修正内容</t>
+  </si>
+  <si>
+    <t>SP0557.fdc</t>
+  </si>
+  <si>
+    <t>AutoConstraint_SP0557.sdc</t>
+  </si>
+  <si>
+    <t>100MHzクロックを115MHzにガードバンディング（0.244ns→約1.3nsスラック確保）</t>
+  </si>
+  <si>
+    <t>再合成後の確認ポイント</t>
+  </si>
+  <si>
+    <r>
+      <t>automake.log</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> の解析により、Synplifyが全PLLクロックを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>個別のクロックグループ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>に配置していることが判明しました：</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>これにより、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>CLK2 ↔ CLK2A 間のパスが "Diff grp" として解析対象外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>になっていました。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>cds.vhd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> のCDR（Clock Data Recovery）回路は CLK2（0°）と CLK2A（90°）の4位相サンプリングに依存しているため、このパスが無制約だと：</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>LE 20%時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: ルーティングリソースが豊富→パスが自然に短い→偶然タイミングが合う</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>LE 80%時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>: ルーティング混雑→パスが長い→CLK2↔CLK2A間のタイミング違反→通信エラー</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>.lpf の FREQUENCY/MULTICYCLE 制約は </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>PAR（配置配線）段階</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> でのみ有効です。しかし、その前段の </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>Synplify合成段階</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> でクロスドメインパスが "Diff grp" として無視されているため、合成後のネットリストが既にタイミング的に最適化されていません。PARがいくらルーティングを最適化しても、合成段階で生成された非最適な論理構造を補いきれません。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>全PLLクロックを同一グループ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>pll_clks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> に統一、CLK2Aに90°位相オフセット（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>-rise 2.500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>）追加、multicycle/false_path制約追加</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>.sdc.bak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> にリネーム（誤ったクロックグループ定義を無効化）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. automake.log</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> で </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>MT420/MT529 警告が消えている</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>こと</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. クロスドメインマトリクスで </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>"Diff grp" が表示されない</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>こと（CLK2↔CLK2A）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. .twr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> タイミングレポートで </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>slack &gt; 1.0ns</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t> であること</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. 実機で LE占有率80%にて </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>通信エラーが発生しない</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>こと</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4038,6 +5017,72 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -4047,7 +5092,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -4088,13 +5133,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4239,6 +5293,78 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -4254,6 +5380,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4662,9 +5792,15 @@
       <c r="F9" s="26"/>
     </row>
     <row r="10" spans="3:6">
-      <c r="C10" s="26"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="27"/>
+      <c r="C10" s="26">
+        <v>6</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>650</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>651</v>
+      </c>
       <c r="F10" s="26"/>
     </row>
     <row r="11" spans="3:6">
@@ -6383,7 +7519,7 @@
     <row r="17" spans="2:5">
       <c r="B17" s="35"/>
     </row>
-    <row r="18" spans="2:5" ht="54">
+    <row r="18" spans="2:5" ht="36">
       <c r="B18" s="31" t="s">
         <v>471</v>
       </c>
@@ -6397,7 +7533,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="166.5">
+    <row r="19" spans="2:5">
       <c r="B19" s="43" t="s">
         <v>475</v>
       </c>
@@ -6411,7 +7547,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="222.75">
+    <row r="20" spans="2:5" ht="36.75">
       <c r="B20" s="43" t="s">
         <v>479</v>
       </c>
@@ -6425,7 +7561,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="204">
+    <row r="21" spans="2:5" ht="36">
       <c r="B21" s="43" t="s">
         <v>482</v>
       </c>
@@ -6439,7 +7575,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="22" spans="2:5" ht="131.25">
+    <row r="22" spans="2:5" ht="36">
       <c r="B22" s="43" t="s">
         <v>485</v>
       </c>
@@ -6453,7 +7589,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="87.75">
+    <row r="23" spans="2:5">
       <c r="B23" s="43" t="s">
         <v>489</v>
       </c>
@@ -6494,7 +7630,7 @@
     <row r="30" spans="2:5">
       <c r="B30" s="35"/>
     </row>
-    <row r="31" spans="2:5" ht="36">
+    <row r="31" spans="2:5">
       <c r="B31" s="31" t="s">
         <v>495</v>
       </c>
@@ -6502,7 +7638,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="32" spans="2:5" ht="222.75">
+    <row r="32" spans="2:5" ht="37.5">
       <c r="B32" s="32" t="s">
         <v>497</v>
       </c>
@@ -6510,7 +7646,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="33" spans="2:4" ht="150">
+    <row r="33" spans="2:4" ht="37.5">
       <c r="B33" s="32" t="s">
         <v>499</v>
       </c>
@@ -6518,7 +7654,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="2:4" ht="168.75">
+    <row r="34" spans="2:4" ht="37.5">
       <c r="B34" s="32" t="s">
         <v>501</v>
       </c>
@@ -6545,7 +7681,7 @@
     <row r="39" spans="2:4">
       <c r="B39" s="35"/>
     </row>
-    <row r="40" spans="2:4" ht="36">
+    <row r="40" spans="2:4">
       <c r="B40" s="31" t="s">
         <v>505</v>
       </c>
@@ -6556,7 +7692,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="41" spans="2:4" ht="56.25">
+    <row r="41" spans="2:4">
       <c r="B41" s="32" t="s">
         <v>508</v>
       </c>
@@ -6567,7 +7703,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="42" spans="2:4" ht="37.5">
+    <row r="42" spans="2:4">
       <c r="B42" s="32" t="s">
         <v>509</v>
       </c>
@@ -6578,7 +7714,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="43" spans="2:4" ht="37.5">
+    <row r="43" spans="2:4">
       <c r="B43" s="32" t="s">
         <v>511</v>
       </c>
@@ -6619,7 +7755,7 @@
     <row r="52" spans="2:5">
       <c r="B52" s="35"/>
     </row>
-    <row r="53" spans="2:5" ht="54">
+    <row r="53" spans="2:5">
       <c r="B53" s="31" t="s">
         <v>105</v>
       </c>
@@ -6633,7 +7769,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="54" spans="2:5" ht="37.5">
+    <row r="54" spans="2:5" ht="36">
       <c r="B54" s="32" t="s">
         <v>518</v>
       </c>
@@ -6647,7 +7783,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="55" spans="2:5" ht="37.5">
+    <row r="55" spans="2:5">
       <c r="B55" s="32" t="s">
         <v>511</v>
       </c>
@@ -6661,7 +7797,7 @@
         <v>-140</v>
       </c>
     </row>
-    <row r="56" spans="2:5" ht="37.5">
+    <row r="56" spans="2:5">
       <c r="B56" s="32" t="s">
         <v>523</v>
       </c>
@@ -7963,4 +9099,708 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D8D6D56-B5C7-4754-AB8D-4CB98E7AAD79}">
+  <dimension ref="B2:E179"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="9" style="28"/>
+    <col min="2" max="2" width="96.5" style="28" customWidth="1"/>
+    <col min="3" max="3" width="24.25" style="28" customWidth="1"/>
+    <col min="4" max="4" width="23.5" style="28" customWidth="1"/>
+    <col min="5" max="5" width="26.375" style="28" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="28"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" ht="24">
+      <c r="B2" s="48" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="28" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" ht="24">
+      <c r="B8" s="48" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" ht="18.75">
+      <c r="B10" s="49" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="50" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="53" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" s="53" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2">
+      <c r="B16" s="53" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="53" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" s="28" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" s="51" t="s">
+        <v>554</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>555</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>556</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="B22" s="52" t="s">
+        <v>558</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>559</v>
+      </c>
+      <c r="D22" s="52" t="s">
+        <v>560</v>
+      </c>
+      <c r="E22" s="52" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23" s="52" t="s">
+        <v>562</v>
+      </c>
+      <c r="C23" s="52" t="s">
+        <v>563</v>
+      </c>
+      <c r="D23" s="52" t="s">
+        <v>560</v>
+      </c>
+      <c r="E23" s="52" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24" s="52" t="s">
+        <v>565</v>
+      </c>
+      <c r="C24" s="52" t="s">
+        <v>566</v>
+      </c>
+      <c r="D24" s="52" t="s">
+        <v>560</v>
+      </c>
+      <c r="E24" s="52" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" s="52" t="s">
+        <v>568</v>
+      </c>
+      <c r="C25" s="52" t="s">
+        <v>566</v>
+      </c>
+      <c r="D25" s="52" t="s">
+        <v>560</v>
+      </c>
+      <c r="E25" s="52" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" s="50" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" ht="18.75">
+      <c r="B29" s="49" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5">
+      <c r="B31" s="50" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="53" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="53" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="53" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="53" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="28" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="53" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="53" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="53" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="53" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="53" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="53" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="53" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="53" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="53" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="53" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" s="53" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="53" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" s="53" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" s="53" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" s="53" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="53" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="53" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="53" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="53" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="53" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="53" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="53" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="53" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="53" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="53" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="53" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80" s="53" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="53" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" s="53" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="53" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" s="53" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="53" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" s="53" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87" s="53" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88" s="53" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90" s="28" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" ht="18.75">
+      <c r="B92" s="49" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94" s="50" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96" s="28" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" ht="18.75">
+      <c r="B98" s="49" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100" s="50" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102" s="28" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103" s="54"/>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104" s="55" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2">
+      <c r="B105" s="55" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107" s="28" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109" s="53" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2">
+      <c r="B110" s="53" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112" s="53" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2">
+      <c r="B113" s="53" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2">
+      <c r="B115" s="53" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2">
+      <c r="B116" s="53" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117" s="53" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2">
+      <c r="B119" s="53" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2">
+      <c r="B120" s="53" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2">
+      <c r="B121" s="53" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" ht="18.75">
+      <c r="B123" s="49" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2">
+      <c r="B125" s="50" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2">
+      <c r="B127" s="53" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="131" spans="2:3" ht="24">
+      <c r="B131" s="48" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="133" spans="2:3">
+      <c r="B133" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="C133" s="51" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3" ht="31.5">
+      <c r="B134" s="56" t="s">
+        <v>625</v>
+      </c>
+      <c r="C134" s="52" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="135" spans="2:3" ht="31.5">
+      <c r="B135" s="56" t="s">
+        <v>627</v>
+      </c>
+      <c r="C135" s="52" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="136" spans="2:3" ht="31.5">
+      <c r="B136" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="C136" s="52" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="139" spans="2:3" ht="24">
+      <c r="B139" s="48" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="140" spans="2:3">
+      <c r="B140" s="54"/>
+    </row>
+    <row r="141" spans="2:3">
+      <c r="B141" s="54" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="142" spans="2:3">
+      <c r="B142" s="54" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="143" spans="2:3">
+      <c r="B143" s="54" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="144" spans="2:3">
+      <c r="B144" s="54" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="145" spans="2:5">
+      <c r="B145" s="57" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="146" spans="2:5">
+      <c r="B146" s="57" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="147" spans="2:5">
+      <c r="B147" s="57" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="148" spans="2:5">
+      <c r="B148" s="54" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="149" spans="2:5">
+      <c r="B149" s="54" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="152" spans="2:5">
+      <c r="B152" s="71"/>
+      <c r="C152" s="71"/>
+      <c r="D152" s="71"/>
+      <c r="E152" s="71"/>
+    </row>
+    <row r="154" spans="2:5" ht="24">
+      <c r="B154" s="58" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="155" spans="2:5" ht="19.5">
+      <c r="B155" s="59" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="156" spans="2:5" ht="18.75">
+      <c r="B156" s="60" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="157" spans="2:5" ht="39">
+      <c r="B157" s="56" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="158" spans="2:5">
+      <c r="B158" s="28" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="159" spans="2:5">
+      <c r="B159" s="28" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="160" spans="2:5">
+      <c r="B160" s="28" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="161" spans="2:3">
+      <c r="B161" s="28" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="162" spans="2:3" ht="58.5">
+      <c r="B162" s="61" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="163" spans="2:3">
+      <c r="B163" s="62"/>
+    </row>
+    <row r="164" spans="2:3" ht="19.5">
+      <c r="B164" s="63" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="165" spans="2:3" ht="19.5">
+      <c r="B165" s="63" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="166" spans="2:3">
+      <c r="B166" s="52"/>
+    </row>
+    <row r="167" spans="2:3" ht="18.75">
+      <c r="B167" s="60" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="168" spans="2:3" ht="78">
+      <c r="B168" s="61" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="169" spans="2:3" ht="24">
+      <c r="B169" s="58" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="170" spans="2:3">
+      <c r="B170" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="C170" s="65" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="171" spans="2:3" ht="95.25" thickBot="1">
+      <c r="B171" s="66" t="s">
+        <v>661</v>
+      </c>
+      <c r="C171" s="67" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="172" spans="2:3" ht="32.25" thickBot="1">
+      <c r="B172" s="66" t="s">
+        <v>662</v>
+      </c>
+      <c r="C172" s="68" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="173" spans="2:3" ht="47.25">
+      <c r="B173" s="66" t="s">
+        <v>66</v>
+      </c>
+      <c r="C173" s="52" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="174" spans="2:3" ht="24">
+      <c r="B174" s="58" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="175" spans="2:3">
+      <c r="B175" s="62"/>
+    </row>
+    <row r="176" spans="2:3" ht="19.5">
+      <c r="B176" s="69" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2" ht="19.5">
+      <c r="B177" s="70" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2" ht="19.5">
+      <c r="B178" s="69" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2" ht="19.5">
+      <c r="B179" s="70" t="s">
+        <v>675</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>